--- a/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Cavigliano_MFH_2005-2014_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>8.855242843513501</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1303.353170495265</v>
       </c>
       <c r="F2" t="n">
-        <v>9.606048782476474</v>
+        <v>4.224431007376617</v>
       </c>
       <c r="G2" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="H2" t="n">
-        <v>8.828582365684182</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="I2" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="J2" t="n">
-        <v>9.606048782476472</v>
+        <v>4.224431007376629</v>
       </c>
       <c r="K2" t="n">
         <v>1303.353170495265</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>8.8552428435135</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1303.353170495265</v>
       </c>
       <c r="F3" t="n">
-        <v>9.606048782476474</v>
+        <v>4.224431007376617</v>
       </c>
       <c r="G3" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="H3" t="n">
-        <v>8.828582365684182</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="I3" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="J3" t="n">
-        <v>9.606048782476472</v>
+        <v>4.224431007376629</v>
       </c>
       <c r="K3" t="n">
         <v>1303.353170495265</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>8.855242843513501</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1303.353170495265</v>
       </c>
       <c r="F4" t="n">
-        <v>9.606048782476474</v>
+        <v>4.224431007376617</v>
       </c>
       <c r="G4" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="H4" t="n">
-        <v>8.828582365684182</v>
+        <v>4.224431007376623</v>
       </c>
       <c r="I4" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="J4" t="n">
-        <v>9.606048782476472</v>
+        <v>4.22443100737663</v>
       </c>
       <c r="K4" t="n">
         <v>1303.353170495265</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>8.855242843513501</v>
+        <v>4.646395468647017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1303.353170495265</v>
       </c>
       <c r="F5" t="n">
-        <v>9.873247154990118</v>
+        <v>4.642986457841381</v>
       </c>
       <c r="G5" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="H5" t="n">
-        <v>8.828582365684182</v>
+        <v>4.967167083763225</v>
       </c>
       <c r="I5" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="J5" t="n">
-        <v>9.873247154990118</v>
+        <v>4.937447917757319</v>
       </c>
       <c r="K5" t="n">
         <v>1303.353170495265</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>9.016347764476247</v>
+        <v>5.046526947329844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1303.353170495265</v>
       </c>
       <c r="F6" t="n">
-        <v>9.964557047097193</v>
+        <v>5.046526947329847</v>
       </c>
       <c r="G6" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="H6" t="n">
-        <v>8.989687286646927</v>
+        <v>5.17957002478963</v>
       </c>
       <c r="I6" t="n">
         <v>1303.353170495265</v>
       </c>
       <c r="J6" t="n">
-        <v>9.875348428094185</v>
+        <v>5.156125358504881</v>
       </c>
       <c r="K6" t="n">
         <v>1303.353170495265</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1.955029755742897</v>
+        <v>4.840875</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.113310245791047</v>
+        <v>4.840875</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.955029755742897</v>
+        <v>2.7566822040751</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.113310245791047</v>
+        <v>2.7566822040751</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1.955029755742897</v>
+        <v>4.840875</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.355214917721327</v>
+        <v>4.840875</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.955029755742897</v>
+        <v>3.355665557290362</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.355214917721327</v>
+        <v>3.355665557290362</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1.955029755742897</v>
+        <v>4.840875</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.454306366557559</v>
+        <v>4.840875</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.955029755742897</v>
+        <v>3.601027202542056</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.454306366557559</v>
+        <v>3.601027202542056</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1.955029755742897</v>
+        <v>4.840875</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.507275280686946</v>
+        <v>4.840875</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.955029755742897</v>
+        <v>3.732184230425073</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.507275280686946</v>
+        <v>3.732184230425073</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Cavigliano_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Cavigliano_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1.955029755742897</v>
+        <v>4.840875</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.540374021944304</v>
+        <v>4.840875</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.955029755742897</v>
+        <v>3.814140460816731</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.540374021944304</v>
+        <v>3.814140460816731</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0008082856447058824</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.0005624430169277007</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0008082856447058827</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0008082856447058824</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.0005624430169277007</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008082856447058827</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008082856447056197</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.0005624430169277007</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0008082856447058827</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008082856447058824</v>
+        <v>0.00059742852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0008434284988235403</v>
+        <v>0.0006325713741176471</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0008082856447058827</v>
+        <v>0.00059742852</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0008434284988235296</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0008082856447058825</v>
+        <v>0.0005974285200000001</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0009143684759203409</v>
+        <v>0.0006325713741176472</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0008082856447058827</v>
+        <v>0.0005974285200000001</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009064971271847815</v>
+        <v>0.000562285665882353</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01493571300000004</v>
+        <v>0.0187752989678081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01120178475000002</v>
+        <v>0.01877646836475896</v>
       </c>
       <c r="G17" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H17" t="n">
-        <v>0.014935713</v>
+        <v>0.01953540659838438</v>
       </c>
       <c r="I17" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01120178475000002</v>
+        <v>0.01953540659838441</v>
       </c>
       <c r="K17" t="n">
         <v>0.1254599892</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0970821345</v>
+        <v>0.05867060428655366</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0970821345</v>
+        <v>0.05892847433661814</v>
       </c>
       <c r="G18" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0970821345</v>
+        <v>0.05314076084838438</v>
       </c>
       <c r="I18" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0970821345</v>
+        <v>0.0531407608483844</v>
       </c>
       <c r="K18" t="n">
         <v>0.1254599892</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0970821345</v>
+        <v>0.05867060428655365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0970821345</v>
+        <v>0.05892847433661814</v>
       </c>
       <c r="G19" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0970821345</v>
+        <v>0.05314076084838438</v>
       </c>
       <c r="I19" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0970821345</v>
+        <v>0.0531407608483844</v>
       </c>
       <c r="K19" t="n">
         <v>0.1254599892</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.08214642149999996</v>
+        <v>0.03989530531874556</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08588034974999997</v>
+        <v>0.04015200597185917</v>
       </c>
       <c r="G20" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0821464215</v>
+        <v>0.03360535425</v>
       </c>
       <c r="I20" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08588034974999997</v>
+        <v>0.03360535425</v>
       </c>
       <c r="K20" t="n">
         <v>0.1254599892</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01493571300000002</v>
+        <v>0.01353514940974029</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003664412183463815</v>
+        <v>0.01353514940974029</v>
       </c>
       <c r="G21" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01533074638239009</v>
+        <v>0.007253581706190993</v>
       </c>
       <c r="I21" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J21" t="n">
-        <v>0.004500742986617012</v>
+        <v>0.007467856500000002</v>
       </c>
       <c r="K21" t="n">
         <v>0.1254599892</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0335894671773914</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.03358863570143181</v>
       </c>
       <c r="G27" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.03307162328314533</v>
       </c>
       <c r="I27" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.03307162328314527</v>
       </c>
       <c r="K27" t="n">
         <v>0.1254599892</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.03841153021344634</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.03815366016338187</v>
       </c>
       <c r="G28" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.04394137365161563</v>
       </c>
       <c r="I28" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.04394137365161561</v>
       </c>
       <c r="K28" t="n">
         <v>0.1254599892</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.03841153021344634</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.03815366016338187</v>
       </c>
       <c r="G29" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.04394137365161563</v>
       </c>
       <c r="I29" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.04398746583148651</v>
       </c>
       <c r="K29" t="n">
         <v>0.1254599892</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.0370778041929125</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.03709348378295834</v>
       </c>
       <c r="G30" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.04107321075</v>
       </c>
       <c r="I30" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.04107321075</v>
       </c>
       <c r="K30" t="n">
         <v>0.1254599892</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.03733928249999999</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.1254599892</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.03733928249999999</v>
       </c>
       <c r="G31" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.04107321075</v>
       </c>
       <c r="I31" t="n">
         <v>0.1254599892</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.04107321075</v>
       </c>
       <c r="K31" t="n">
         <v>0.1254599892</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>1.510845590298948</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.8760259957180686</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1.510845590298948</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>1.510845590298948</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>1.065105809656171</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.510845590298948</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>1.510845590298948</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>1.14297417009828</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.510845590298948</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>1.510845590298948</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>1.185185177587068</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.510845590298948</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>1.510845590298948</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>1.212010377770798</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.510845590298948</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.08274345437010744</v>
+        <v>0.07685544674353172</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08262571856660732</v>
+        <v>0.07860603473812736</v>
       </c>
       <c r="G47" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08864930800824301</v>
+        <v>0.07685544674353174</v>
       </c>
       <c r="I47" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J47" t="n">
-        <v>0.08870864385566445</v>
+        <v>0.07860199142996449</v>
       </c>
       <c r="K47" t="n">
         <v>0.393220431269406</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.08274345437010744</v>
+        <v>0.07685544674353172</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08262571856660732</v>
+        <v>0.07860603473812736</v>
       </c>
       <c r="G48" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08864930800824301</v>
+        <v>0.07685544674353174</v>
       </c>
       <c r="I48" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J48" t="n">
-        <v>0.08870864385566445</v>
+        <v>0.07860199142996449</v>
       </c>
       <c r="K48" t="n">
         <v>0.393220431269406</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08274345437010744</v>
+        <v>0.07685544674353172</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F49" t="n">
-        <v>0.08262571856660732</v>
+        <v>0.07860603473812736</v>
       </c>
       <c r="G49" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08864930800824301</v>
+        <v>0.07685544674353174</v>
       </c>
       <c r="I49" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J49" t="n">
-        <v>0.08870864385566445</v>
+        <v>0.07860199142996449</v>
       </c>
       <c r="K49" t="n">
         <v>0.393220431269406</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.08333028717005202</v>
+        <v>0.08958834860182129</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1128523767003537</v>
+        <v>0.08451805825360183</v>
       </c>
       <c r="G52" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.08571217972719992</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.1233748520521515</v>
       </c>
-      <c r="H52" t="n">
-        <v>0.07589222448484535</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.393220431269406</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.1079243410758182</v>
+        <v>0.07930341025557916</v>
       </c>
       <c r="K52" t="n">
         <v>0.1233748520521515</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.08333028717005202</v>
+        <v>0.08958834860182129</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1128523767003537</v>
+        <v>0.08451805825360183</v>
       </c>
       <c r="G53" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.08571217972719992</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.1622975385497232</v>
       </c>
-      <c r="H53" t="n">
-        <v>0.07589222448484535</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.393220431269406</v>
-      </c>
       <c r="J53" t="n">
-        <v>0.1079243410758182</v>
+        <v>0.07930341025557916</v>
       </c>
       <c r="K53" t="n">
         <v>0.1622975385497232</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08333028717005202</v>
+        <v>0.08958834860182129</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1128523767003537</v>
+        <v>0.08451805825360181</v>
       </c>
       <c r="G54" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.08571217972719992</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.1796434032208704</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.07589222448484535</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.393220431269406</v>
-      </c>
       <c r="J54" t="n">
-        <v>0.1079243410758182</v>
+        <v>0.07930341025557916</v>
       </c>
       <c r="K54" t="n">
         <v>0.1796434032208704</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1003055467472591</v>
+        <v>0.1037837955142476</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1002491198147981</v>
+        <v>0.09985760185307689</v>
       </c>
       <c r="G55" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1040316423461334</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.1890045897266559</v>
       </c>
-      <c r="H55" t="n">
-        <v>0.09705150653864326</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.393220431269406</v>
-      </c>
       <c r="J55" t="n">
-        <v>0.09705150653864325</v>
+        <v>0.09898573147816002</v>
       </c>
       <c r="K55" t="n">
         <v>0.1890045897266559</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1003055467472591</v>
+        <v>0.1037837955142476</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1002491198147981</v>
+        <v>0.09985760185307689</v>
       </c>
       <c r="G56" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1040316423461334</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.1947833101010531</v>
       </c>
-      <c r="H56" t="n">
-        <v>0.09705150653864326</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.393220431269406</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.09705150653864326</v>
+        <v>0.09898573147816003</v>
       </c>
       <c r="K56" t="n">
         <v>0.1947833101010531</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.1233748520521515</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.393220431269406</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.1622975385497232</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.393220431269406</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.1796434032208704</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.393220431269406</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.1890045897266559</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.393220431269406</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>0.393220431269406</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>0.1947833101010531</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.393220431269406</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.04165486433224449</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F62" t="n">
-        <v>0.03996142594201272</v>
+        <v>0.02601037766956329</v>
       </c>
       <c r="G62" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H62" t="n">
-        <v>0.04177983532206943</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="I62" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0388065362774911</v>
+        <v>0.02602427675325323</v>
       </c>
       <c r="K62" t="n">
         <v>0.393220431269406</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.04165486433224449</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03996142594201272</v>
+        <v>0.02601037766956329</v>
       </c>
       <c r="G63" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04177983532206943</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="I63" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0388065362774911</v>
+        <v>0.02602427675325323</v>
       </c>
       <c r="K63" t="n">
         <v>0.393220431269406</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.04165486433224449</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03996142594201272</v>
+        <v>0.02601037766956329</v>
       </c>
       <c r="G64" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H64" t="n">
-        <v>0.04177983532206943</v>
+        <v>0.02515579377374211</v>
       </c>
       <c r="I64" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0388065362774911</v>
+        <v>0.02602427675325323</v>
       </c>
       <c r="K64" t="n">
         <v>0.393220431269406</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.08223170204324426</v>
+        <v>0.04106720781234048</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07751623376565854</v>
+        <v>0.0449934014735112</v>
       </c>
       <c r="G65" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H65" t="n">
-        <v>0.085610713241685</v>
+        <v>0.03958806581093791</v>
       </c>
       <c r="I65" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J65" t="n">
-        <v>0.08071384704181345</v>
+        <v>0.04481020624236068</v>
       </c>
       <c r="K65" t="n">
         <v>0.393220431269406</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.08223170204324426</v>
+        <v>0.04106720781234048</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F66" t="n">
-        <v>0.07784339796341952</v>
+        <v>0.0449934014735112</v>
       </c>
       <c r="G66" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="H66" t="n">
-        <v>0.085610713241685</v>
+        <v>0.03958806581093791</v>
       </c>
       <c r="I66" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J66" t="n">
-        <v>0.08145917664115097</v>
+        <v>0.04481020624236068</v>
       </c>
       <c r="K66" t="n">
         <v>0.393220431269406</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.01216979161743226</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01216979161743226</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01884799125909522</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01884799125909522</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02325070115108479</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02325070115108479</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.02645666815862746</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.02645666815862746</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.02893833454834726</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02893833454834726</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.04673920961372249</v>
+        <v>0.04443503828298165</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.04690015674078427</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01216979161743226</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H77" t="n">
-        <v>0.04827141866079358</v>
+        <v>0.04831120715760299</v>
       </c>
       <c r="I77" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J77" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.05210494896327987</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01216979161743226</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.04673920961372249</v>
+        <v>0.04443503828298165</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.04690015674078427</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01884799125909522</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H78" t="n">
-        <v>0.04827141866079358</v>
+        <v>0.04831120715760299</v>
       </c>
       <c r="I78" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.05210494896327987</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01884799125909522</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.04673920961372249</v>
+        <v>0.04443503828298165</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>0.393220431269406</v>
       </c>
       <c r="F79" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.04690015674078427</v>
       </c>
       <c r="G79" t="n">
-        <v>0.02325070115108479</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H79" t="n">
-        <v>0.04827141866079358</v>
+        <v>0.04831120715760299</v>
       </c>
       <c r="I79" t="n">
         <v>0.393220431269406</v>
       </c>
       <c r="J79" t="n">
-        <v>0.01550889143826374</v>
+        <v>0.05210494896327987</v>
       </c>
       <c r="K79" t="n">
-        <v>0.02325070115108479</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.02645666815862746</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02645666815862746</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.02893833454834726</v>
+        <v>0.393220431269406</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.02893833454834726</v>
+        <v>0.393220431269406</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
